--- a/metricas_realizadas/Prog-Concurrente/Analisis de metricas/Resultados_Resumen_metricas_2C_ 2026.xlsx
+++ b/metricas_realizadas/Prog-Concurrente/Analisis de metricas/Resultados_Resumen_metricas_2C_ 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_code_ia\metricas_realizadas\Prog-Concurrente\Analisis de metricas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61461AD7-89FE-4BB2-92FB-275A3282F688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AC456C-A687-47CA-8DD2-9F040A56AE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Grupo</t>
   </si>
@@ -125,6 +125,18 @@
   </si>
   <si>
     <t>Sol 5.6</t>
+  </si>
+  <si>
+    <t>ReparaBarrio</t>
+  </si>
+  <si>
+    <t>SDD (SPEC → PLAN → hitos + refinamientos)</t>
+  </si>
+  <si>
+    <t>SOL 6.1</t>
+  </si>
+  <si>
+    <t>GPT- Codex (CLI)</t>
   </si>
 </sst>
 </file>
@@ -629,6 +641,21 @@
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/metricas_realizadas/Prog-Concurrente/Analisis de metricas/Resultados_Resumen_metricas_2C_ 2026.xlsx
+++ b/metricas_realizadas/Prog-Concurrente/Analisis de metricas/Resultados_Resumen_metricas_2C_ 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_code_ia\metricas_realizadas\Prog-Concurrente\Analisis de metricas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AC456C-A687-47CA-8DD2-9F040A56AE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95BA014-947C-4CEE-A82D-3C2C992420BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>Grupo</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>M2</t>
-  </si>
-  <si>
-    <t>M3</t>
   </si>
   <si>
     <t>M4</t>
@@ -137,13 +134,55 @@
   </si>
   <si>
     <t>GPT- Codex (CLI)</t>
+  </si>
+  <si>
+    <t>Simulador de Centro Logístico Concurrente</t>
+  </si>
+  <si>
+    <t>Gemini (planificación) + Claude Code con gentle-ai (código)</t>
+  </si>
+  <si>
+    <t>Gemini 3.1 Pro / Claude Opus 5.5</t>
+  </si>
+  <si>
+    <t>Meta-prompting + Chain of Thought + Role prompting</t>
+  </si>
+  <si>
+    <t>2C-26-M3-AN-Gemini</t>
+  </si>
+  <si>
+    <t>2C-26-M3-CC-Opus</t>
+  </si>
+  <si>
+    <t>2C-26-M3-CC-Composer</t>
+  </si>
+  <si>
+    <t>Cinema Reservation System</t>
+  </si>
+  <si>
+    <t>Antigravity</t>
+  </si>
+  <si>
+    <t>Gemini 3.8</t>
+  </si>
+  <si>
+    <t>Cursor</t>
+  </si>
+  <si>
+    <t>Claude Opus 5.5</t>
+  </si>
+  <si>
+    <t>Composer 2.5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +201,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -193,9 +237,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -219,9 +265,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Millares 2" xfId="3" xr:uid="{255834D3-54D1-4A75-958C-2B7E7D4C3517}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{AAC9BC59-3EE6-4EA5-9D9D-B29D4408C468}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{22E9AC32-DABF-44DF-BC50-DECEF85EC746}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -499,9 +547,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="21.6328125" customWidth="1"/>
     <col min="2" max="2" width="35.54296875" customWidth="1"/>
     <col min="3" max="3" width="25.7265625" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
@@ -519,16 +568,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -546,115 +595,191 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="A4" s="3"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="6"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A5" s="3"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
         <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/metricas_realizadas/Prog-Concurrente/Analisis de metricas/Resultados_Resumen_metricas_2C_ 2026.xlsx
+++ b/metricas_realizadas/Prog-Concurrente/Analisis de metricas/Resultados_Resumen_metricas_2C_ 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_code_ia\metricas_realizadas\Prog-Concurrente\Analisis de metricas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95BA014-947C-4CEE-A82D-3C2C992420BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAA8D29-0E84-4519-93D4-2599EBC544C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>Grupo</t>
   </si>
@@ -173,6 +173,15 @@
   </si>
   <si>
     <t>Composer 2.5</t>
+  </si>
+  <si>
+    <t>Banco concurrente v2 (refinado)</t>
+  </si>
+  <si>
+    <t>Claude Code</t>
+  </si>
+  <si>
+    <t>Sonnet</t>
   </si>
 </sst>
 </file>
@@ -711,11 +720,21 @@
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
